--- a/A 题/result3.xlsx
+++ b/A 题/result3.xlsx
@@ -562,19 +562,19 @@
         <v>28</v>
       </c>
       <c r="D2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E2" t="n">
         <v>11</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>52</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>14</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>13</v>
-      </c>
-      <c r="H2" t="n">
-        <v>27</v>
       </c>
       <c r="I2" t="n">
         <v>26</v>
@@ -645,10 +645,10 @@
         <v>5</v>
       </c>
       <c r="T3" t="n">
+        <v>48</v>
+      </c>
+      <c r="U3" t="n">
         <v>24</v>
-      </c>
-      <c r="U3" t="n">
-        <v>48</v>
       </c>
       <c r="V3" t="n">
         <v>37</v>
@@ -701,27 +701,30 @@
         <v>4</v>
       </c>
       <c r="L4" t="n">
+        <v>38</v>
+      </c>
+      <c r="M4" t="n">
         <v>39</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>34</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>35</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>36</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>49</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>22</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>23</v>
       </c>
     </row>
@@ -733,58 +736,55 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="K5" t="n">
         <v>43</v>
       </c>
       <c r="L5" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="N5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P5" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="Q5" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>22</v>
-      </c>
-      <c r="T5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1173,205 +1173,205 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" t="n">
+        <v>57</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H2" t="n">
+        <v>23</v>
+      </c>
+      <c r="I2" t="n">
         <v>15</v>
       </c>
-      <c r="C2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="J2" t="n">
         <v>23</v>
       </c>
-      <c r="E2" t="n">
-        <v>39</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="K2" t="n">
+        <v>24</v>
+      </c>
+      <c r="L2" t="n">
+        <v>25</v>
+      </c>
+      <c r="M2" t="n">
+        <v>26</v>
+      </c>
+      <c r="N2" t="n">
+        <v>25</v>
+      </c>
+      <c r="O2" t="n">
+        <v>26</v>
+      </c>
+      <c r="P2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q2" t="n">
         <v>42</v>
       </c>
-      <c r="G2" t="n">
-        <v>54</v>
-      </c>
-      <c r="H2" t="n">
-        <v>43</v>
-      </c>
-      <c r="I2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="R2" t="n">
         <v>36</v>
       </c>
-      <c r="M2" t="n">
-        <v>25</v>
-      </c>
-      <c r="N2" t="n">
-        <v>24</v>
-      </c>
-      <c r="O2" t="n">
-        <v>38</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
+        <v>91</v>
+      </c>
+      <c r="T2" t="n">
+        <v>73</v>
+      </c>
+      <c r="U2" t="n">
+        <v>82</v>
+      </c>
+      <c r="V2" t="n">
+        <v>83</v>
+      </c>
+      <c r="W2" t="n">
+        <v>41</v>
+      </c>
+      <c r="X2" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>58</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>59</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>61</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>62</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>71</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>71</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>81</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>71</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>69</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>78</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>77</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>76</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>86</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>87</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>88</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>89</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>99</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>98</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>97</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>93</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>92</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>91</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>92</v>
+      </c>
+      <c r="BE2" t="n">
         <v>94</v>
       </c>
-      <c r="Q2" t="n">
-        <v>98</v>
-      </c>
-      <c r="R2" t="n">
-        <v>92</v>
-      </c>
-      <c r="S2" t="n">
-        <v>38</v>
-      </c>
-      <c r="T2" t="n">
-        <v>69</v>
-      </c>
-      <c r="U2" t="n">
-        <v>57</v>
-      </c>
-      <c r="V2" t="n">
+      <c r="BF2" t="n">
+        <v>84</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>75</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>68</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>67</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>74</v>
+      </c>
+      <c r="BK2" t="n">
         <v>64</v>
       </c>
-      <c r="W2" t="n">
-        <v>58</v>
-      </c>
-      <c r="X2" t="n">
-        <v>86</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>79</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>71</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>87</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>86</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>77</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>89</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>53</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>33</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM2" t="n">
+      <c r="BL2" t="n">
+        <v>28</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>66</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BO2" t="n">
         <v>2</v>
       </c>
-      <c r="AN2" t="n">
-        <v>47</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ2" t="n">
+      <c r="BP2" t="n">
         <v>1</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>76</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>83</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>91</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>92</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>73</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>92</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>90</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>55</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>66</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>59</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>35</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>27</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>25</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>35</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>44</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -1379,220 +1379,220 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>14</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
         <v>12</v>
       </c>
-      <c r="C3" t="n">
-        <v>40</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="P3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>12</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>11</v>
+      </c>
+      <c r="T3" t="n">
+        <v>20</v>
+      </c>
+      <c r="U3" t="n">
         <v>31</v>
       </c>
-      <c r="E3" t="n">
+      <c r="V3" t="n">
+        <v>30</v>
+      </c>
+      <c r="W3" t="n">
+        <v>29</v>
+      </c>
+      <c r="X3" t="n">
+        <v>37</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>92</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>94</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>86</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>87</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>88</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>79</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>79</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>76</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>47</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR3" t="n">
         <v>48</v>
       </c>
-      <c r="F3" t="n">
-        <v>62</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="AS3" t="n">
+        <v>39</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>43</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AY3" t="n">
         <v>33</v>
       </c>
-      <c r="J3" t="n">
-        <v>29</v>
-      </c>
-      <c r="K3" t="n">
-        <v>26</v>
-      </c>
-      <c r="L3" t="n">
-        <v>37</v>
-      </c>
-      <c r="M3" t="n">
-        <v>30</v>
-      </c>
-      <c r="N3" t="n">
-        <v>21</v>
-      </c>
-      <c r="O3" t="n">
-        <v>41</v>
-      </c>
-      <c r="P3" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>90</v>
-      </c>
-      <c r="R3" t="n">
-        <v>93</v>
-      </c>
-      <c r="S3" t="n">
-        <v>99</v>
-      </c>
-      <c r="T3" t="n">
-        <v>82</v>
-      </c>
-      <c r="U3" t="n">
-        <v>96</v>
-      </c>
-      <c r="V3" t="n">
-        <v>75</v>
-      </c>
-      <c r="W3" t="n">
-        <v>97</v>
-      </c>
-      <c r="X3" t="n">
-        <v>88</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>87</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>53</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>51</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>49</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>94</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>64</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>76</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>71</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>45</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>56</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="BA3" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="BB3" t="n">
         <v>66</v>
       </c>
       <c r="BC3" t="n">
+        <v>64</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF3" t="n">
         <v>65</v>
       </c>
-      <c r="BD3" t="n">
-        <v>64</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>74</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>84</v>
-      </c>
       <c r="BG3" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="BH3" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="BI3" t="n">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="BJ3" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="BK3" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="BL3" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="BM3" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="BN3" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="BO3" t="n">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="BP3" t="n">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="BQ3" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="BR3" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BS3" t="n">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="BT3" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="BU3" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +1606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1770,34 +1770,19 @@
           <t>31th Inspection Point</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>32th Inspection Point</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>33th Inspection Point</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>34th Inspection Point</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
         <v>42</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="E2" t="n">
         <v>34</v>
@@ -1827,69 +1812,60 @@
         <v>77</v>
       </c>
       <c r="N2" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="O2" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="P2" t="n">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="Q2" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="R2" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="S2" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="T2" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="U2" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="V2" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="W2" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="Y2" t="n">
         <v>23</v>
       </c>
       <c r="Z2" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="AA2" t="n">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="AB2" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="AC2" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="AD2" t="n">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="AE2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AF2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>96</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>39</v>
-      </c>
-      <c r="AI2" t="n">
         <v>55</v>
       </c>
     </row>
@@ -1898,85 +1874,82 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C3" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="E3" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="G3" t="n">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="H3" t="n">
+        <v>33</v>
+      </c>
+      <c r="I3" t="n">
         <v>10</v>
       </c>
-      <c r="I3" t="n">
-        <v>33</v>
-      </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="L3" t="n">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="M3" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="N3" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="O3" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="P3" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="Q3" t="n">
         <v>54</v>
       </c>
       <c r="R3" t="n">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="S3" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
+        <v>26</v>
+      </c>
+      <c r="U3" t="n">
         <v>9</v>
       </c>
-      <c r="U3" t="n">
-        <v>26</v>
-      </c>
       <c r="V3" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="W3" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="X3" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="Z3" t="n">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="AA3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -1987,7 +1960,7 @@
         <v>43</v>
       </c>
       <c r="C4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" t="n">
         <v>81</v>
@@ -2011,55 +1984,61 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="L4" t="n">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="M4" t="n">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="N4" t="n">
         <v>85</v>
       </c>
       <c r="O4" t="n">
+        <v>12</v>
+      </c>
+      <c r="P4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>32</v>
+      </c>
+      <c r="R4" t="n">
         <v>82</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>75</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>49</v>
       </c>
-      <c r="R4" t="n">
-        <v>75</v>
-      </c>
-      <c r="S4" t="n">
-        <v>49</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>86</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>63</v>
       </c>
-      <c r="V4" t="n">
-        <v>15</v>
-      </c>
       <c r="W4" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="X4" t="n">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="Y4" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="Z4" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="AA4" t="n">
-        <v>30</v>
+        <v>5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>41</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -2109,45 +2088,39 @@
         <v>67</v>
       </c>
       <c r="P5" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q5" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="R5" t="n">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="S5" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
+        <v>60</v>
+      </c>
+      <c r="U5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>60</v>
-      </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="W5" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="X5" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="Y5" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="Z5" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="AA5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AC5" t="n">
         <v>81</v>
       </c>
     </row>
@@ -2156,79 +2129,91 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
+        <v>40</v>
+      </c>
+      <c r="C6" t="n">
         <v>52</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>36</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>47</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>53</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>6</v>
       </c>
-      <c r="G6" t="n">
-        <v>28</v>
-      </c>
       <c r="H6" t="n">
+        <v>46</v>
+      </c>
+      <c r="I6" t="n">
+        <v>50</v>
+      </c>
+      <c r="J6" t="n">
+        <v>46</v>
+      </c>
+      <c r="K6" t="n">
+        <v>56</v>
+      </c>
+      <c r="L6" t="n">
         <v>19</v>
       </c>
-      <c r="I6" t="n">
-        <v>54</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
+        <v>46</v>
+      </c>
+      <c r="N6" t="n">
         <v>70</v>
       </c>
-      <c r="K6" t="n">
-        <v>72</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
+        <v>38</v>
+      </c>
+      <c r="P6" t="n">
         <v>17</v>
       </c>
-      <c r="M6" t="n">
+      <c r="Q6" t="n">
         <v>74</v>
       </c>
-      <c r="N6" t="n">
+      <c r="R6" t="n">
         <v>20</v>
       </c>
-      <c r="O6" t="n">
+      <c r="S6" t="n">
         <v>78</v>
       </c>
-      <c r="P6" t="n">
+      <c r="T6" t="n">
         <v>32</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="U6" t="n">
         <v>4</v>
       </c>
-      <c r="R6" t="n">
+      <c r="V6" t="n">
         <v>21</v>
       </c>
-      <c r="S6" t="n">
+      <c r="W6" t="n">
         <v>86</v>
       </c>
-      <c r="T6" t="n">
+      <c r="X6" t="n">
         <v>97</v>
       </c>
-      <c r="U6" t="n">
+      <c r="Y6" t="n">
+        <v>69</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA6" t="n">
         <v>68</v>
       </c>
-      <c r="V6" t="n">
-        <v>90</v>
-      </c>
-      <c r="W6" t="n">
-        <v>69</v>
-      </c>
-      <c r="X6" t="n">
+      <c r="AB6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AC6" t="n">
         <v>30</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AD6" t="n">
         <v>24</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2502,151 +2487,151 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
+        <v>64</v>
+      </c>
+      <c r="C2" t="n">
         <v>109</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>11</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>5</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>16</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>128</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>112</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>62</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>105</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>112</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>28</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
+        <v>18</v>
+      </c>
+      <c r="O2" t="n">
+        <v>21</v>
+      </c>
+      <c r="P2" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>46</v>
+      </c>
+      <c r="R2" t="n">
+        <v>118</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>46</v>
+      </c>
+      <c r="U2" t="n">
+        <v>80</v>
+      </c>
+      <c r="V2" t="n">
+        <v>37</v>
+      </c>
+      <c r="W2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X2" t="n">
+        <v>37</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>121</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>78</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>125</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>59</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>126</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>108</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>114</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>117</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>112</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>62</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO2" t="n">
         <v>115</v>
       </c>
-      <c r="N2" t="n">
-        <v>28</v>
-      </c>
-      <c r="O2" t="n">
-        <v>62</v>
-      </c>
-      <c r="P2" t="n">
-        <v>112</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>114</v>
-      </c>
-      <c r="R2" t="n">
-        <v>108</v>
-      </c>
-      <c r="S2" t="n">
-        <v>8</v>
-      </c>
-      <c r="T2" t="n">
-        <v>126</v>
-      </c>
-      <c r="U2" t="n">
-        <v>30</v>
-      </c>
-      <c r="V2" t="n">
-        <v>59</v>
-      </c>
-      <c r="W2" t="n">
-        <v>90</v>
-      </c>
-      <c r="X2" t="n">
-        <v>125</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>78</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>121</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>33</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>37</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>37</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>117</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>93</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>118</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
         <v>50</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AQ2" t="n">
         <v>130</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>39</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
         <v>71</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AT2" t="n">
         <v>39</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
         <v>41</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AV2" t="n">
         <v>1</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AW2" t="n">
         <v>76</v>
       </c>
-      <c r="AW2" t="n">
-        <v>61</v>
-      </c>
       <c r="AX2" t="n">
-        <v>64</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3">
@@ -2654,150 +2639,147 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
+        <v>64</v>
+      </c>
+      <c r="C3" t="n">
+        <v>124</v>
+      </c>
+      <c r="D3" t="n">
         <v>86</v>
       </c>
-      <c r="C3" t="n">
-        <v>64</v>
-      </c>
-      <c r="D3" t="n">
-        <v>124</v>
-      </c>
       <c r="E3" t="n">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="F3" t="n">
+        <v>26</v>
+      </c>
+      <c r="G3" t="n">
+        <v>88</v>
+      </c>
+      <c r="H3" t="n">
         <v>127</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>19</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>27</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>100</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>31</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>17</v>
-      </c>
-      <c r="L3" t="n">
-        <v>54</v>
-      </c>
-      <c r="M3" t="n">
-        <v>35</v>
       </c>
       <c r="N3" t="n">
         <v>54</v>
       </c>
       <c r="O3" t="n">
+        <v>35</v>
+      </c>
+      <c r="P3" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q3" t="n">
         <v>4</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>42</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
+        <v>40</v>
+      </c>
+      <c r="T3" t="n">
         <v>44</v>
-      </c>
-      <c r="R3" t="n">
-        <v>40</v>
-      </c>
-      <c r="S3" t="n">
-        <v>47</v>
-      </c>
-      <c r="T3" t="n">
-        <v>40</v>
       </c>
       <c r="U3" t="n">
         <v>23</v>
       </c>
       <c r="V3" t="n">
+        <v>47</v>
+      </c>
+      <c r="W3" t="n">
+        <v>40</v>
+      </c>
+      <c r="X3" t="n">
         <v>122</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>55</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>14</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>10</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
         <v>102</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>6</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AD3" t="n">
         <v>60</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AE3" t="n">
         <v>120</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>49</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>58</v>
       </c>
       <c r="AF3" t="n">
         <v>49</v>
       </c>
       <c r="AG3" t="n">
+        <v>58</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>49</v>
+      </c>
+      <c r="AI3" t="n">
         <v>106</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
         <v>38</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AK3" t="n">
         <v>79</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AL3" t="n">
         <v>95</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AM3" t="n">
         <v>116</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>24</v>
       </c>
       <c r="AN3" t="n">
         <v>15</v>
       </c>
       <c r="AO3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>29</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AR3" t="n">
         <v>89</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AS3" t="n">
         <v>110</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AT3" t="n">
         <v>68</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AU3" t="n">
         <v>63</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AV3" t="n">
         <v>70</v>
       </c>
-      <c r="AU3" t="n">
-        <v>97</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>26</v>
-      </c>
       <c r="AW3" t="n">
-        <v>88</v>
-      </c>
-      <c r="AX3" t="n">
         <v>86</v>
       </c>
     </row>
@@ -2851,81 +2833,84 @@
         <v>39</v>
       </c>
       <c r="Q4" t="n">
+        <v>129</v>
+      </c>
+      <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>116</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>81</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>12</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>87</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>12</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>73</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>74</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>75</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>52</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>9</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>57</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>101</v>
       </c>
       <c r="AD4" t="n">
         <v>82</v>
       </c>
       <c r="AE4" t="n">
+        <v>101</v>
+      </c>
+      <c r="AF4" t="n">
         <v>111</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>123</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>101</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
         <v>119</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AJ4" t="n">
         <v>84</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>36</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AL4" t="n">
         <v>32</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AM4" t="n">
         <v>113</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AN4" t="n">
         <v>89</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AO4" t="n">
         <v>98</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AP4" t="n">
         <v>25</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AQ4" t="n">
         <v>48</v>
       </c>
     </row>
@@ -2946,7 +2931,7 @@
         <v>64</v>
       </c>
       <c r="F5" t="n">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="G5" t="n">
         <v>107</v>
@@ -2955,13 +2940,13 @@
         <v>104</v>
       </c>
       <c r="I5" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="J5" t="n">
         <v>34</v>
       </c>
       <c r="K5" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
         <v>100</v>
@@ -3012,10 +2997,10 @@
         <v>53</v>
       </c>
       <c r="AB5" t="n">
+        <v>72</v>
+      </c>
+      <c r="AC5" t="n">
         <v>49</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>72</v>
       </c>
       <c r="AD5" t="n">
         <v>91</v>

--- a/A 题/result3.xlsx
+++ b/A 题/result3.xlsx
@@ -606,58 +606,58 @@
         <v>23</v>
       </c>
       <c r="G3" t="n">
+        <v>44</v>
+      </c>
+      <c r="H3" t="n">
+        <v>46</v>
+      </c>
+      <c r="I3" t="n">
+        <v>37</v>
+      </c>
+      <c r="J3" t="n">
+        <v>48</v>
+      </c>
+      <c r="K3" t="n">
+        <v>24</v>
+      </c>
+      <c r="L3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>15</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+      <c r="R3" t="n">
+        <v>28</v>
+      </c>
+      <c r="S3" t="n">
+        <v>27</v>
+      </c>
+      <c r="T3" t="n">
+        <v>28</v>
+      </c>
+      <c r="U3" t="n">
+        <v>46</v>
+      </c>
+      <c r="V3" t="n">
+        <v>16</v>
+      </c>
+      <c r="W3" t="n">
+        <v>50</v>
+      </c>
+      <c r="X3" t="n">
         <v>20</v>
-      </c>
-      <c r="H3" t="n">
-        <v>50</v>
-      </c>
-      <c r="I3" t="n">
-        <v>16</v>
-      </c>
-      <c r="J3" t="n">
-        <v>46</v>
-      </c>
-      <c r="K3" t="n">
-        <v>28</v>
-      </c>
-      <c r="L3" t="n">
-        <v>27</v>
-      </c>
-      <c r="M3" t="n">
-        <v>28</v>
-      </c>
-      <c r="N3" t="n">
-        <v>25</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>15</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>48</v>
-      </c>
-      <c r="U3" t="n">
-        <v>24</v>
-      </c>
-      <c r="V3" t="n">
-        <v>37</v>
-      </c>
-      <c r="W3" t="n">
-        <v>46</v>
-      </c>
-      <c r="X3" t="n">
-        <v>44</v>
       </c>
       <c r="Y3" t="n">
         <v>50</v>
@@ -733,58 +733,58 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>45</v>
+      </c>
+      <c r="E5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F5" t="n">
+        <v>41</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" t="n">
+        <v>43</v>
+      </c>
+      <c r="K5" t="n">
+        <v>33</v>
+      </c>
+      <c r="L5" t="n">
+        <v>43</v>
+      </c>
+      <c r="M5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N5" t="n">
+        <v>40</v>
+      </c>
+      <c r="O5" t="n">
+        <v>39</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>22</v>
+      </c>
+      <c r="R5" t="n">
+        <v>21</v>
+      </c>
+      <c r="S5" t="n">
         <v>7</v>
-      </c>
-      <c r="C5" t="n">
-        <v>21</v>
-      </c>
-      <c r="D5" t="n">
-        <v>22</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>39</v>
-      </c>
-      <c r="G5" t="n">
-        <v>40</v>
-      </c>
-      <c r="H5" t="n">
-        <v>15</v>
-      </c>
-      <c r="I5" t="n">
-        <v>43</v>
-      </c>
-      <c r="J5" t="n">
-        <v>33</v>
-      </c>
-      <c r="K5" t="n">
-        <v>43</v>
-      </c>
-      <c r="L5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M5" t="n">
-        <v>9</v>
-      </c>
-      <c r="N5" t="n">
-        <v>8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>41</v>
-      </c>
-      <c r="P5" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>45</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU3"/>
+  <dimension ref="A1:BS3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,16 +1157,6 @@
           <t>70th Inspection Point</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>71th Inspection Point</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>72th Inspection Point</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1182,31 +1172,31 @@
         <v>57</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I2" t="n">
         <v>23</v>
       </c>
-      <c r="I2" t="n">
-        <v>15</v>
-      </c>
       <c r="J2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="N2" t="n">
         <v>25</v>
@@ -1224,153 +1214,159 @@
         <v>36</v>
       </c>
       <c r="S2" t="n">
+        <v>94</v>
+      </c>
+      <c r="T2" t="n">
         <v>91</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>73</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>82</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>83</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>41</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>40</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>50</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>49</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>58</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>59</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>61</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>62</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>71</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
         <v>72</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>71</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
         <v>81</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AJ2" t="n">
         <v>71</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AK2" t="n">
         <v>70</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>69</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AM2" t="n">
         <v>78</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AN2" t="n">
         <v>77</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AO2" t="n">
         <v>76</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
         <v>85</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AQ2" t="n">
         <v>86</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>95</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
         <v>87</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AT2" t="n">
         <v>88</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
         <v>89</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AV2" t="n">
         <v>90</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AW2" t="n">
         <v>99</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AX2" t="n">
         <v>98</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AY2" t="n">
         <v>97</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="AZ2" t="n">
         <v>34</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>13</v>
-      </c>
       <c r="BA2" t="n">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="BB2" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="BD2" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="BE2" t="n">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="BF2" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="BG2" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="BH2" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="BI2" t="n">
         <v>67</v>
       </c>
       <c r="BJ2" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="BK2" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="BL2" t="n">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="BM2" t="n">
+        <v>92</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>93</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>91</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>92</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>66</v>
       </c>
-      <c r="BN2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP2" t="n">
+      <c r="BR2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1394,22 +1390,22 @@
         <v>18</v>
       </c>
       <c r="G3" t="n">
+        <v>27</v>
+      </c>
+      <c r="H3" t="n">
         <v>9</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>8</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>6</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>14</v>
       </c>
       <c r="M3" t="n">
         <v>4</v>
@@ -1547,34 +1543,34 @@
         <v>3</v>
       </c>
       <c r="BF3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG3" t="n">
         <v>65</v>
       </c>
-      <c r="BG3" t="n">
-        <v>50</v>
-      </c>
       <c r="BH3" t="n">
+        <v>53</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>52</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>51</v>
+      </c>
+      <c r="BK3" t="n">
         <v>96</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>51</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>52</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>53</v>
       </c>
       <c r="BL3" t="n">
         <v>63</v>
       </c>
       <c r="BM3" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="BN3" t="n">
         <v>54</v>
       </c>
       <c r="BO3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="BP3" t="n">
         <v>33</v>
@@ -1587,12 +1583,6 @@
       </c>
       <c r="BS3" t="n">
         <v>35</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>27</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1782,91 +1772,91 @@
         <v>42</v>
       </c>
       <c r="D2" t="n">
+        <v>34</v>
+      </c>
+      <c r="E2" t="n">
+        <v>61</v>
+      </c>
+      <c r="F2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G2" t="n">
+        <v>52</v>
+      </c>
+      <c r="H2" t="n">
+        <v>45</v>
+      </c>
+      <c r="I2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J2" t="n">
+        <v>98</v>
+      </c>
+      <c r="K2" t="n">
+        <v>95</v>
+      </c>
+      <c r="L2" t="n">
+        <v>28</v>
+      </c>
+      <c r="M2" t="n">
+        <v>37</v>
+      </c>
+      <c r="N2" t="n">
+        <v>93</v>
+      </c>
+      <c r="O2" t="n">
+        <v>77</v>
+      </c>
+      <c r="P2" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>76</v>
+      </c>
+      <c r="R2" t="n">
+        <v>58</v>
+      </c>
+      <c r="S2" t="n">
+        <v>88</v>
+      </c>
+      <c r="T2" t="n">
+        <v>84</v>
+      </c>
+      <c r="U2" t="n">
+        <v>23</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W2" t="n">
+        <v>89</v>
+      </c>
+      <c r="X2" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>35</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>96</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>39</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF2" t="n">
         <v>43</v>
-      </c>
-      <c r="E2" t="n">
-        <v>34</v>
-      </c>
-      <c r="F2" t="n">
-        <v>61</v>
-      </c>
-      <c r="G2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H2" t="n">
-        <v>52</v>
-      </c>
-      <c r="I2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K2" t="n">
-        <v>98</v>
-      </c>
-      <c r="L2" t="n">
-        <v>95</v>
-      </c>
-      <c r="M2" t="n">
-        <v>77</v>
-      </c>
-      <c r="N2" t="n">
-        <v>28</v>
-      </c>
-      <c r="O2" t="n">
-        <v>37</v>
-      </c>
-      <c r="P2" t="n">
-        <v>93</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>59</v>
-      </c>
-      <c r="R2" t="n">
-        <v>76</v>
-      </c>
-      <c r="S2" t="n">
-        <v>58</v>
-      </c>
-      <c r="T2" t="n">
-        <v>88</v>
-      </c>
-      <c r="U2" t="n">
-        <v>84</v>
-      </c>
-      <c r="V2" t="n">
-        <v>23</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2</v>
-      </c>
-      <c r="X2" t="n">
-        <v>89</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>35</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>35</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>96</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>39</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -1969,75 +1959,72 @@
         <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="G4" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="H4" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="I4" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="K4" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="L4" t="n">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="N4" t="n">
         <v>85</v>
       </c>
       <c r="O4" t="n">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="Q4" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="R4" t="n">
-        <v>82</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="T4" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="U4" t="n">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="V4" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="W4" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="X4" t="n">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="Y4" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="Z4" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="AA4" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="AB4" t="n">
-        <v>41</v>
-      </c>
-      <c r="AC4" t="n">
         <v>25</v>
       </c>
     </row>
@@ -2046,82 +2033,85 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>44</v>
+      </c>
+      <c r="D5" t="n">
+        <v>52</v>
+      </c>
+      <c r="E5" t="n">
+        <v>36</v>
+      </c>
+      <c r="F5" t="n">
+        <v>57</v>
+      </c>
+      <c r="G5" t="n">
+        <v>98</v>
+      </c>
+      <c r="H5" t="n">
+        <v>94</v>
+      </c>
+      <c r="I5" t="n">
+        <v>53</v>
+      </c>
+      <c r="J5" t="n">
+        <v>79</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>12</v>
+      </c>
+      <c r="M5" t="n">
+        <v>13</v>
+      </c>
+      <c r="N5" t="n">
+        <v>67</v>
+      </c>
+      <c r="O5" t="n">
+        <v>87</v>
+      </c>
+      <c r="P5" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>18</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>60</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>71</v>
+      </c>
+      <c r="V5" t="n">
+        <v>68</v>
+      </c>
+      <c r="W5" t="n">
+        <v>83</v>
+      </c>
+      <c r="X5" t="n">
+        <v>51</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>81</v>
+      </c>
+      <c r="AA5" t="n">
         <v>22</v>
       </c>
-      <c r="C5" t="n">
+      <c r="AB5" t="n">
         <v>41</v>
-      </c>
-      <c r="D5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E5" t="n">
-        <v>44</v>
-      </c>
-      <c r="F5" t="n">
-        <v>52</v>
-      </c>
-      <c r="G5" t="n">
-        <v>36</v>
-      </c>
-      <c r="H5" t="n">
-        <v>57</v>
-      </c>
-      <c r="I5" t="n">
-        <v>98</v>
-      </c>
-      <c r="J5" t="n">
-        <v>94</v>
-      </c>
-      <c r="K5" t="n">
-        <v>53</v>
-      </c>
-      <c r="L5" t="n">
-        <v>79</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" t="n">
-        <v>13</v>
-      </c>
-      <c r="O5" t="n">
-        <v>67</v>
-      </c>
-      <c r="P5" t="n">
-        <v>87</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>62</v>
-      </c>
-      <c r="R5" t="n">
-        <v>18</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>60</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>71</v>
-      </c>
-      <c r="W5" t="n">
-        <v>68</v>
-      </c>
-      <c r="X5" t="n">
-        <v>83</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>51</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>81</v>
       </c>
     </row>
     <row r="6">
@@ -2201,10 +2191,10 @@
         <v>69</v>
       </c>
       <c r="Z6" t="n">
+        <v>68</v>
+      </c>
+      <c r="AA6" t="n">
         <v>90</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>68</v>
       </c>
       <c r="AB6" t="n">
         <v>80</v>
@@ -2517,94 +2507,94 @@
         <v>105</v>
       </c>
       <c r="L2" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M2" t="n">
         <v>28</v>
       </c>
       <c r="N2" t="n">
+        <v>62</v>
+      </c>
+      <c r="O2" t="n">
+        <v>112</v>
+      </c>
+      <c r="P2" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>90</v>
+      </c>
+      <c r="R2" t="n">
+        <v>125</v>
+      </c>
+      <c r="S2" t="n">
+        <v>90</v>
+      </c>
+      <c r="T2" t="n">
+        <v>78</v>
+      </c>
+      <c r="U2" t="n">
+        <v>121</v>
+      </c>
+      <c r="V2" t="n">
+        <v>33</v>
+      </c>
+      <c r="W2" t="n">
+        <v>37</v>
+      </c>
+      <c r="X2" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>118</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>93</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG2" t="n">
         <v>18</v>
       </c>
-      <c r="O2" t="n">
-        <v>21</v>
-      </c>
-      <c r="P2" t="n">
-        <v>93</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>46</v>
-      </c>
-      <c r="R2" t="n">
-        <v>118</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>46</v>
-      </c>
-      <c r="U2" t="n">
-        <v>80</v>
-      </c>
-      <c r="V2" t="n">
-        <v>37</v>
-      </c>
-      <c r="W2" t="n">
-        <v>22</v>
-      </c>
-      <c r="X2" t="n">
-        <v>37</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>33</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>121</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>78</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>125</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="AH2" t="n">
         <v>59</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
         <v>30</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
         <v>126</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AK2" t="n">
         <v>8</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AL2" t="n">
         <v>108</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AM2" t="n">
         <v>114</v>
       </c>
-      <c r="AK2" t="n">
-        <v>117</v>
-      </c>
-      <c r="AL2" t="n">
+      <c r="AN2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO2" t="n">
         <v>112</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>62</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>115</v>
       </c>
       <c r="AP2" t="n">
         <v>50</v>
@@ -2639,10 +2629,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
+        <v>124</v>
+      </c>
+      <c r="C3" t="n">
         <v>64</v>
-      </c>
-      <c r="C3" t="n">
-        <v>124</v>
       </c>
       <c r="D3" t="n">
         <v>86</v>
@@ -2687,99 +2677,96 @@
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="S3" t="n">
+        <v>44</v>
+      </c>
+      <c r="T3" t="n">
+        <v>122</v>
+      </c>
+      <c r="U3" t="n">
+        <v>47</v>
+      </c>
+      <c r="V3" t="n">
         <v>40</v>
       </c>
-      <c r="T3" t="n">
-        <v>44</v>
-      </c>
-      <c r="U3" t="n">
-        <v>23</v>
-      </c>
-      <c r="V3" t="n">
-        <v>47</v>
-      </c>
       <c r="W3" t="n">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="X3" t="n">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="Y3" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AA3" t="n">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="AB3" t="n">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="AC3" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AE3" t="n">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="AF3" t="n">
+        <v>58</v>
+      </c>
+      <c r="AG3" t="n">
         <v>49</v>
       </c>
-      <c r="AG3" t="n">
-        <v>58</v>
-      </c>
       <c r="AH3" t="n">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="AI3" t="n">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="AJ3" t="n">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="AK3" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="AL3" t="n">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="AM3" t="n">
-        <v>116</v>
+        <v>15</v>
       </c>
       <c r="AN3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO3" t="n">
         <v>15</v>
       </c>
-      <c r="AO3" t="n">
-        <v>24</v>
-      </c>
       <c r="AP3" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="AQ3" t="n">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="AR3" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="AS3" t="n">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="AT3" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="AU3" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="AV3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AW3" t="n">
         <v>86</v>
       </c>
     </row>
@@ -2788,130 +2775,130 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C4" t="n">
+        <v>88</v>
+      </c>
+      <c r="D4" t="n">
+        <v>124</v>
+      </c>
+      <c r="E4" t="n">
+        <v>129</v>
+      </c>
+      <c r="F4" t="n">
+        <v>45</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="n">
+        <v>28</v>
+      </c>
+      <c r="I4" t="n">
+        <v>66</v>
+      </c>
+      <c r="J4" t="n">
+        <v>85</v>
+      </c>
+      <c r="K4" t="n">
+        <v>90</v>
+      </c>
+      <c r="L4" t="n">
+        <v>59</v>
+      </c>
+      <c r="M4" t="n">
+        <v>83</v>
+      </c>
+      <c r="N4" t="n">
+        <v>117</v>
+      </c>
+      <c r="O4" t="n">
+        <v>39</v>
+      </c>
+      <c r="P4" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
+        <v>116</v>
+      </c>
+      <c r="S4" t="n">
+        <v>81</v>
+      </c>
+      <c r="T4" t="n">
+        <v>12</v>
+      </c>
+      <c r="U4" t="n">
+        <v>87</v>
+      </c>
+      <c r="V4" t="n">
+        <v>12</v>
+      </c>
+      <c r="W4" t="n">
+        <v>73</v>
+      </c>
+      <c r="X4" t="n">
+        <v>74</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>57</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>82</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>101</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>111</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>123</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>101</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>119</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>84</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>113</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>89</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>98</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>97</v>
-      </c>
-      <c r="C4" t="n">
-        <v>26</v>
-      </c>
-      <c r="D4" t="n">
-        <v>88</v>
-      </c>
-      <c r="E4" t="n">
-        <v>124</v>
-      </c>
-      <c r="F4" t="n">
-        <v>129</v>
-      </c>
-      <c r="G4" t="n">
-        <v>45</v>
-      </c>
-      <c r="H4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I4" t="n">
-        <v>28</v>
-      </c>
-      <c r="J4" t="n">
-        <v>66</v>
-      </c>
-      <c r="K4" t="n">
-        <v>85</v>
-      </c>
-      <c r="L4" t="n">
-        <v>90</v>
-      </c>
-      <c r="M4" t="n">
-        <v>59</v>
-      </c>
-      <c r="N4" t="n">
-        <v>83</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
-      <c r="P4" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>129</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>116</v>
-      </c>
-      <c r="T4" t="n">
-        <v>81</v>
-      </c>
-      <c r="U4" t="n">
-        <v>12</v>
-      </c>
-      <c r="V4" t="n">
-        <v>87</v>
-      </c>
-      <c r="W4" t="n">
-        <v>12</v>
-      </c>
-      <c r="X4" t="n">
-        <v>73</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>74</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>52</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>57</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>82</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>101</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>111</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>123</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>101</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>119</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>84</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>113</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>89</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>98</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>48</v>
       </c>
     </row>
     <row r="5">
@@ -2919,55 +2906,55 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="C5" t="n">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F5" t="n">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="G5" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H5" t="n">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="I5" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="J5" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
+        <v>15</v>
+      </c>
+      <c r="M5" t="n">
+        <v>24</v>
+      </c>
+      <c r="N5" t="n">
         <v>100</v>
       </c>
-      <c r="M5" t="n">
-        <v>15</v>
-      </c>
-      <c r="N5" t="n">
-        <v>24</v>
-      </c>
       <c r="O5" t="n">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="P5" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="Q5" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="R5" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="S5" t="n">
         <v>126</v>
@@ -2988,7 +2975,7 @@
         <v>96</v>
       </c>
       <c r="Y5" t="n">
-        <v>122</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="n">
         <v>51</v>
@@ -3046,6 +3033,9 @@
       </c>
       <c r="AR5" t="n">
         <v>68</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
